--- a/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -613,6 +613,18 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>State Farm 2026-09-18</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Bundled home+auto (was Travelers home / Geico auto). HOME share $1105.46 on 524 INSURANCE 50/50 U1/U2 (yellow proxy from Feb $157.53/$145.25). AUTO share $1019.33 + Geico credit $540.89 EXCLUDED personal. No 2025 Travelers found. No Sep–Dec SF on Prime. Not tax advice.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -625,6 +625,18 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Grove Collaborative 2026-09-18</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>User: “grove orders” = Grove Collaborative, not 827 N Grove the house. Prime $791.21 already on 524 Unit 2 SUPPLIES (8 charges). HD/Lowe’s/IKEA 1/3 $604.12 stays on 827 N Grove the house (Q5), not mixed into Grove Collaborative. Betty’s Pizza / KS Grove is personal dining. Not tax advice.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q1–4 CONFIRMED. March HD → 524 repairs 50/50. Remaining HD/Lowe’s/IKEA 1/3 524 / 1/3 personal / 1/3 Grove. ComEd yellow — REMIND JACOB: double-check with Megan (checking ACH or extra check). Canva + Park Chicago + Field Museum $53 EPGC. Frame Up framing + LAMA/Hindman inventory. Soldier Field parking $57 and Extra Space $360 still HOLD. Not tax advice.</t>
+          <t>Q1–4 CONFIRMED. Grove Collaborative (not 827 N Grove) → 524 Unit 2 SUPPLIES $791.21. March HD → 524 repairs 50/50. Remaining HD/Lowe’s/IKEA 1/3 524 / 1/3 personal / 1/3 827 N Grove the house. ComEd yellow — REMIND JACOB: double-check with Megan (checking ACH or extra check). Canva + Park Chicago + Field Museum $53 EPGC. Frame Up framing + LAMA/Hindman inventory. Soldier Field parking $57 and Extra Space $360 still HOLD. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
@@ -61,11 +61,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -637,6 +640,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Checking inflows 2026-09-18</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>JSC 9922 + joint 0203 full-year eStmts. GCM BOM $21500.00 → EPGC Consultant. Reimburse $5214.69 excluded. 216 Oak Park rent cash $19500.00 (Delach / Ava yellow / Joan yellow). Bear Creek $38000.00 + UTMA Thomas $10000.00 not income. Freeman’s CIBC $11,000 HOLD. Not tax advice.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/_SOURCE_2025.xlsx
@@ -66,7 +66,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,19 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>JSC 9922 + joint 0203 full-year eStmts. GCM BOM $21500.00 → EPGC Consultant. Reimburse $5214.69 excluded. 216 Oak Park rent cash $19500.00 (Delach / Ava yellow / Joan yellow). Bear Creek $38000.00 + UTMA Thomas $10000.00 not income. Freeman’s CIBC $11,000 HOLD. Not tax advice.</t>
+          <t>JSC 9922 + joint 0203 full-year eStmts. GCM BOM $21500.00 → GCM tab + Income E7 only (NOT EPGC Consultant). Reimburse $5214.69 excluded (May 22 CONFIRMED). 216 Oak Park rent cash $19500.00 (Ava co-tenant CONFIRMED). Vacant Oct + half Nov. Joan repair $675 → INTERIOR Dec. Bear Creek $38000.00 gift to Jake from parents. UTMA Thomas $10000.00 not income. Freeman’s Sale 6428 $11,000 Art Sales (check to Megan). 8507 WAIT-MEGAN. Not tax advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Checking answers 2026-09-18</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Q1 Ava co-tenant keep. Q2 vacant Oct + half Nov. Q3 Joan half-Nov WAIT 8507; 12/1 Zelle OUT $675 repair. Q4 GCM off EPGC Consultant. Q5 May 22 reimbursement. Q6 Bear Creek $38k to Jake from parents. Q7 Freeman’s $11k art settlement to Megan. Q8 Megan sending 8507 statements.</t>
         </is>
       </c>
     </row>
